--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484575_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484575_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>J. CARPIO MANEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5817</v>
+        <v>-0.1771</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1202</v>
+        <v>-0.0551</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5385</v>
+        <v>-0.122</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.158</v>
+        <v>0.2075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2656</v>
+        <v>-0.3053</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.4237</v>
+        <v>0.5128</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0478</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.554</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5062</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.2059</v>
+        <v>0.2075</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2884</v>
+        <v>-0.3053</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.9175</v>
+        <v>0.5128</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9321</v>
+        <v>0.1833</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.7647</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9705</v>
+        <v>-0.5679</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2413</v>
+        <v>-0.0551</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2118</v>
+        <v>-0.5128</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7014</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5.0783</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CARPIO MANEZ</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1771</v>
+        <v>-0.3701</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0551</v>
+        <v>0.8868</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.122</v>
+        <v>-1.2569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2075</v>
+        <v>-3.158</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3053</v>
+        <v>0.2656</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5128</v>
+        <v>-3.4237</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.0478</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.5062</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2075</v>
+        <v>-4.2059</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3053</v>
+        <v>-1.2884</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5128</v>
+        <v>-2.9175</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.7647</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1833</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5679</v>
+        <v>0.0187</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0551</v>
+        <v>-0.4747</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5128</v>
+        <v>0.4934</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.7014</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>5.0783</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2843</v>
+        <v>-0.71</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4474</v>
+        <v>1.0217</v>
       </c>
       <c r="F5" t="n">
         <v>-1.7317</v>
@@ -844,10 +844,10 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>0.641</v>
+        <v>0.2153</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4193</v>
+        <v>-0.0064</v>
       </c>
       <c r="U5" t="n">
         <v>0.2217</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3455</v>
+        <v>-2.1721</v>
       </c>
       <c r="E6" t="n">
         <v>2.201</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5465</v>
+        <v>-4.3731</v>
       </c>
       <c r="G6" t="n">
         <v>-2.3479</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2592</v>
+        <v>-1.0858</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2949</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9643</v>
+        <v>-0.7909</v>
       </c>
       <c r="V6" t="n">
         <v>2.5444</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4591</v>
+        <v>-3.305</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1669</v>
+        <v>-1.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2922</v>
+        <v>-2.1931</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1216</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2642</v>
+        <v>-0.1101</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2767</v>
+        <v>-0.2217</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.1116</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2566</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7036</v>
+        <v>-3.6541</v>
       </c>
       <c r="E8" t="n">
         <v>-1.2534</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4502</v>
+        <v>-2.4007</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7653</v>
@@ -1078,13 +1078,13 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1216</v>
+        <v>-1.072</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7362</v>
+        <v>-0.6867</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6335</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4721</v>
+        <v>-3.98</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1196</v>
+        <v>-4.7761</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6475</v>
+        <v>0.7961</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9845</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2207</v>
+        <v>-0.7285</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.193</v>
+        <v>-0.8495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0276</v>
+        <v>0.121</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7991</v>
+        <v>-4.4279</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.043</v>
+        <v>-2.7956</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7561</v>
+        <v>-1.6323</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3946</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2658</v>
+        <v>0.1054</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6056</v>
+        <v>-0.3582</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3397</v>
+        <v>0.4636</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3219</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.138</v>
+        <v>-4.6827</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7857</v>
+        <v>-2.1272</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3523</v>
+        <v>-2.5555</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2255</v>
+        <v>-1.8533</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0007</v>
+        <v>-0.8563</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2248</v>
+        <v>-0.997</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3279</v>
+        <v>0.2016</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.155</v>
+        <v>0.1084</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1729</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8976</v>
+        <v>-2.0549</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8457</v>
+        <v>-0.9647</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0519</v>
+        <v>-1.0902</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0303</v>
+        <v>-1.1959</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4419</v>
+        <v>-0.4962</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5884</v>
+        <v>-0.6997</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3011</v>
+        <v>-1.267</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3011</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1416</v>
+        <v>-5.1846</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5118</v>
+        <v>-3.8818</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6298</v>
+        <v>-1.3028</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8533</v>
+        <v>-4.2255</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8563</v>
+        <v>-1.0007</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.997</v>
+        <v>-3.2248</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2016</v>
+        <v>-1.3279</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1084</v>
+        <v>-0.155</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09320000000000001</v>
+        <v>-1.1729</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0549</v>
+        <v>-2.8976</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9647</v>
+        <v>-0.8457</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0902</v>
+        <v>-2.0519</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6548</v>
+        <v>-1.0769</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8808</v>
+        <v>-0.5381</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.774</v>
+        <v>-0.5389</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.267</v>
+        <v>0.3011</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-28.3136</v>
+        <v>-28.0385</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.5418</v>
+        <v>-11.2665</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.7718</v>
+        <v>-16.772</v>
       </c>
       <c r="G13" t="n">
         <v>-24.5378</v>
@@ -1468,13 +1468,13 @@
         <v>11.9118</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.773</v>
+        <v>-5.4977</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9554</v>
+        <v>-3.6802</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8176</v>
+        <v>-1.8177</v>
       </c>
       <c r="V13" t="n">
         <v>4.745999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5559</v>
+        <v>7.1188</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6054</v>
+        <v>7.3169</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0495</v>
+        <v>-0.1981</v>
       </c>
       <c r="G14" t="n">
         <v>0.6656</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5683</v>
+        <v>1.1312</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1712</v>
+        <v>0.8827</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3971</v>
+        <v>0.2485</v>
       </c>
       <c r="V14" t="n">
         <v>3.4894</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3614</v>
+        <v>6.4874</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0112</v>
+        <v>4.8831</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3501</v>
+        <v>1.6044</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2807</v>
+        <v>4.5817</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5146</v>
+        <v>0.392</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7661</v>
+        <v>4.1897</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6659</v>
+        <v>4.6643</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9317</v>
+        <v>1.1796</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7342</v>
+        <v>3.4847</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6148</v>
+        <v>-0.0827</v>
       </c>
       <c r="N15" t="n">
-        <v>0.583</v>
+        <v>-0.7876</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0318</v>
+        <v>0.705</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8424</v>
+        <v>0.2564</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5732</v>
+        <v>0.2187</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2693</v>
+        <v>0.0377</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8055</v>
+        <v>4.7193</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4984</v>
+        <v>1.7612</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3071</v>
+        <v>2.9581</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5817</v>
+        <v>3.2807</v>
       </c>
       <c r="H16" t="n">
-        <v>0.392</v>
+        <v>2.5146</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1897</v>
+        <v>0.7661</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6643</v>
+        <v>2.6659</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1796</v>
+        <v>1.9317</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4847</v>
+        <v>0.7342</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0827</v>
+        <v>0.6148</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7876</v>
+        <v>0.583</v>
       </c>
       <c r="O16" t="n">
-        <v>0.705</v>
+        <v>0.0318</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4255</v>
+        <v>1.2004</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1659</v>
+        <v>0.3232</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2596</v>
+        <v>0.8772</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5086</v>
+        <v>4.463</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1705</v>
+        <v>6.0213</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3381</v>
+        <v>-1.5582</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5163</v>
+        <v>7.0808</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8111</v>
+        <v>0.7171</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7052</v>
+        <v>6.3637</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4708</v>
+        <v>7.452</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4706</v>
+        <v>1.5047</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0002</v>
+        <v>5.9473</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0456</v>
+        <v>-0.3712</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6594</v>
+        <v>-0.7876</v>
       </c>
       <c r="O17" t="n">
-        <v>0.705</v>
+        <v>0.4164</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9977</v>
+        <v>0.2564</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1712</v>
+        <v>0.1086</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8265</v>
+        <v>0.1478</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2774</v>
+        <v>-3.7905</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2774</v>
+        <v>-0.6231</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.1674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8802</v>
+        <v>3.684</v>
       </c>
       <c r="E18" t="n">
-        <v>5.6367</v>
+        <v>1.5936</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7564</v>
+        <v>2.0904</v>
       </c>
       <c r="G18" t="n">
-        <v>7.0808</v>
+        <v>2.5163</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7171</v>
+        <v>0.8111</v>
       </c>
       <c r="I18" t="n">
-        <v>6.3637</v>
+        <v>1.7052</v>
       </c>
       <c r="J18" t="n">
-        <v>7.452</v>
+        <v>2.4708</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5047</v>
+        <v>1.4706</v>
       </c>
       <c r="L18" t="n">
-        <v>5.9473</v>
+        <v>1.0002</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3712</v>
+        <v>0.0456</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7876</v>
+        <v>-0.6594</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4164</v>
+        <v>0.705</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9163</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3264</v>
+        <v>1.1731</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.276</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0504</v>
+        <v>0.5788</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.7905</v>
+        <v>1.2774</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6231</v>
+        <v>1.2774</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.1674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3998</v>
+        <v>1.4478</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2072</v>
+        <v>1.3995</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1926</v>
+        <v>0.0483</v>
       </c>
       <c r="G19" t="n">
         <v>3.8394</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8274</v>
+        <v>0.8754</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1297</v>
+        <v>0.0626</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9571</v>
+        <v>0.8128</v>
       </c>
       <c r="V19" t="n">
         <v>-2.5339</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9502</v>
+        <v>1.0144</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9502</v>
+        <v>-0.3446</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.359</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9502</v>
+        <v>-0.7575</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3251</v>
+        <v>-0.5654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6251</v>
+        <v>-0.1922</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9502</v>
+        <v>-0.7145</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3251</v>
+        <v>0.1826</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6251</v>
+        <v>-0.8971</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.043</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.748</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.4446</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.3699</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.0746</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4345</v>
+        <v>0.9502</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8254</v>
+        <v>0.9502</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2599</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7575</v>
+        <v>0.9502</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5654</v>
+        <v>0.3251</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1922</v>
+        <v>0.6251</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7145</v>
+        <v>0.9502</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1826</v>
+        <v>0.3251</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8971</v>
+        <v>0.6251</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.043</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.748</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1353</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1108</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0244</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0324</v>
+        <v>0.1336</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4578</v>
+        <v>-3.0732</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4254</v>
+        <v>3.2068</v>
       </c>
       <c r="G23" t="n">
         <v>2.671</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1737</v>
+        <v>0.3397</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8808</v>
+        <v>-0.4962</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0546</v>
+        <v>0.8359</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3115</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9424</v>
+        <v>-0.2721</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2676</v>
+        <v>-1.1715</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3252</v>
+        <v>0.8994</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3091</v>
@@ -2326,13 +2326,13 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3271</v>
+        <v>0.3431</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2949</v>
+        <v>-0.1987</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0323</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5889</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8579</v>
+        <v>-2.0419</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0072</v>
+        <v>-3.8149</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1493</v>
+        <v>1.773</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2315</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4223</v>
+        <v>0.3937</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2398</v>
+        <v>-0.0475</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1825</v>
+        <v>0.4412</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6543</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>28.3136</v>
+        <v>28.9547</v>
       </c>
       <c r="E26" t="n">
         <v>16.7718</v>
       </c>
       <c r="F26" t="n">
-        <v>11.5418</v>
+        <v>12.1831</v>
       </c>
       <c r="G26" t="n">
         <v>24.5378</v>
@@ -2458,7 +2458,7 @@
         <v>21.4344</v>
       </c>
       <c r="K26" t="n">
-        <v>7.9683</v>
+        <v>7.968299999999998</v>
       </c>
       <c r="L26" t="n">
         <v>13.466</v>
@@ -2482,19 +2482,19 @@
         <v>14.6606</v>
       </c>
       <c r="S26" t="n">
-        <v>5.772900000000002</v>
+        <v>6.413999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8177</v>
+        <v>1.8176</v>
       </c>
       <c r="U26" t="n">
-        <v>3.955399999999999</v>
+        <v>4.5963</v>
       </c>
       <c r="V26" t="n">
         <v>-4.745700000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>5.431400000000001</v>
+        <v>5.4314</v>
       </c>
       <c r="X26" t="n">
         <v>-10.1773</v>
